--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113426895</v>
+        <v>113426900</v>
       </c>
       <c r="B11" t="n">
-        <v>90414</v>
+        <v>90063</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,32 +1848,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762907</v>
+        <v>762875</v>
       </c>
       <c r="R11" t="n">
-        <v>7092583</v>
+        <v>7092628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,7 +1912,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1919,7 +1921,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113426900</v>
+        <v>113426895</v>
       </c>
       <c r="B12" t="n">
-        <v>90047</v>
+        <v>90430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1954,34 +1955,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762875</v>
+        <v>762907</v>
       </c>
       <c r="R12" t="n">
-        <v>7092628</v>
+        <v>7092583</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,7 +2017,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,6 +2026,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113426900</v>
+        <v>113426895</v>
       </c>
       <c r="B11" t="n">
-        <v>90063</v>
+        <v>90442</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,34 +1848,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762875</v>
+        <v>762907</v>
       </c>
       <c r="R11" t="n">
-        <v>7092628</v>
+        <v>7092583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1912,7 +1910,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,6 +1919,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1939,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113426895</v>
+        <v>113426900</v>
       </c>
       <c r="B12" t="n">
-        <v>90430</v>
+        <v>90075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1955,32 +1954,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762907</v>
+        <v>762875</v>
       </c>
       <c r="R12" t="n">
-        <v>7092583</v>
+        <v>7092628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2017,7 +2018,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,7 +2027,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1835,7 +1835,7 @@
         <v>113426895</v>
       </c>
       <c r="B11" t="n">
-        <v>90442</v>
+        <v>90464</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>113426900</v>
       </c>
       <c r="B12" t="n">
-        <v>90075</v>
+        <v>90097</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113426895</v>
+        <v>113426900</v>
       </c>
       <c r="B11" t="n">
-        <v>90464</v>
+        <v>90101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,32 +1848,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762907</v>
+        <v>762875</v>
       </c>
       <c r="R11" t="n">
-        <v>7092583</v>
+        <v>7092628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,7 +1912,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1919,7 +1921,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113426900</v>
+        <v>113426895</v>
       </c>
       <c r="B12" t="n">
-        <v>90097</v>
+        <v>90468</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1954,34 +1955,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762875</v>
+        <v>762907</v>
       </c>
       <c r="R12" t="n">
-        <v>7092628</v>
+        <v>7092583</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,7 +2017,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,6 +2026,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1835,7 +1835,7 @@
         <v>113426900</v>
       </c>
       <c r="B11" t="n">
-        <v>90101</v>
+        <v>90107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>113426895</v>
       </c>
       <c r="B12" t="n">
-        <v>90468</v>
+        <v>90474</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113426900</v>
+        <v>113426895</v>
       </c>
       <c r="B11" t="n">
-        <v>90107</v>
+        <v>90481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,34 +1848,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762875</v>
+        <v>762907</v>
       </c>
       <c r="R11" t="n">
-        <v>7092628</v>
+        <v>7092583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1912,7 +1910,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,6 +1919,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1939,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113426895</v>
+        <v>113426900</v>
       </c>
       <c r="B12" t="n">
-        <v>90474</v>
+        <v>90114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1955,32 +1954,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762907</v>
+        <v>762875</v>
       </c>
       <c r="R12" t="n">
-        <v>7092583</v>
+        <v>7092628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2017,7 +2018,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,7 +2027,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1835,7 +1835,7 @@
         <v>113426895</v>
       </c>
       <c r="B11" t="n">
-        <v>90481</v>
+        <v>90486</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>113426900</v>
       </c>
       <c r="B12" t="n">
-        <v>90114</v>
+        <v>90117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113426895</v>
+        <v>113426900</v>
       </c>
       <c r="B11" t="n">
-        <v>90486</v>
+        <v>90148</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,32 +1848,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762907</v>
+        <v>762875</v>
       </c>
       <c r="R11" t="n">
-        <v>7092583</v>
+        <v>7092628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,7 +1912,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1919,7 +1921,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113426900</v>
+        <v>113426895</v>
       </c>
       <c r="B12" t="n">
-        <v>90117</v>
+        <v>90517</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1954,34 +1955,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762875</v>
+        <v>762907</v>
       </c>
       <c r="R12" t="n">
-        <v>7092628</v>
+        <v>7092583</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2018,7 +2017,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,6 +2026,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113426900</v>
+        <v>113426895</v>
       </c>
       <c r="B11" t="n">
-        <v>90148</v>
+        <v>90518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,34 +1848,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762875</v>
+        <v>762907</v>
       </c>
       <c r="R11" t="n">
-        <v>7092628</v>
+        <v>7092583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1912,7 +1910,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,6 +1919,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1939,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113426895</v>
+        <v>113426900</v>
       </c>
       <c r="B12" t="n">
-        <v>90517</v>
+        <v>90149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1955,32 +1954,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelån Ersboda, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762907</v>
+        <v>762875</v>
       </c>
       <c r="R12" t="n">
-        <v>7092583</v>
+        <v>7092628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2017,7 +2018,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,7 +2027,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -1835,7 +1835,7 @@
         <v>113426895</v>
       </c>
       <c r="B11" t="n">
-        <v>90518</v>
+        <v>90522</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>113426900</v>
       </c>
       <c r="B12" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -2916,7 +2916,7 @@
         <v>118479869</v>
       </c>
       <c r="B20" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,6 +3033,117 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121587747</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tavelån-Ersboda, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>762874</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7092631</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33004-2022 artfynd.xlsx
+++ b/artfynd/A 33004-2022 artfynd.xlsx
@@ -3038,7 +3038,7 @@
         <v>121587747</v>
       </c>
       <c r="B21" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
